--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181587</v>
+        <v>120181606</v>
       </c>
       <c r="B2" t="n">
-        <v>78689</v>
+        <v>74570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>1776</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446769</v>
+        <v>446711</v>
       </c>
       <c r="R2" t="n">
-        <v>7167211</v>
+        <v>7167230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181606</v>
+        <v>120181587</v>
       </c>
       <c r="B3" t="n">
-        <v>74570</v>
+        <v>78689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1776</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446711</v>
+        <v>446769</v>
       </c>
       <c r="R3" t="n">
-        <v>7167230</v>
+        <v>7167211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181606</v>
+        <v>120181587</v>
       </c>
       <c r="B2" t="n">
-        <v>74570</v>
+        <v>78705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1776</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446711</v>
+        <v>446769</v>
       </c>
       <c r="R2" t="n">
-        <v>7167230</v>
+        <v>7167211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181587</v>
+        <v>120181984</v>
       </c>
       <c r="B3" t="n">
-        <v>78689</v>
+        <v>74646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446769</v>
+        <v>446742</v>
       </c>
       <c r="R3" t="n">
-        <v>7167211</v>
+        <v>7167235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181984</v>
+        <v>120181606</v>
       </c>
       <c r="B4" t="n">
-        <v>74630</v>
+        <v>74586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446742</v>
+        <v>446711</v>
       </c>
       <c r="R4" t="n">
-        <v>7167235</v>
+        <v>7167230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181587</v>
+        <v>120181984</v>
       </c>
       <c r="B2" t="n">
-        <v>78705</v>
+        <v>74646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446769</v>
+        <v>446742</v>
       </c>
       <c r="R2" t="n">
-        <v>7167211</v>
+        <v>7167235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181984</v>
+        <v>120181587</v>
       </c>
       <c r="B3" t="n">
-        <v>74646</v>
+        <v>78705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446742</v>
+        <v>446769</v>
       </c>
       <c r="R3" t="n">
-        <v>7167235</v>
+        <v>7167211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181984</v>
+        <v>120181587</v>
       </c>
       <c r="B2" t="n">
-        <v>74646</v>
+        <v>78705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446742</v>
+        <v>446769</v>
       </c>
       <c r="R2" t="n">
-        <v>7167235</v>
+        <v>7167211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181587</v>
+        <v>120181984</v>
       </c>
       <c r="B3" t="n">
-        <v>78705</v>
+        <v>74646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446769</v>
+        <v>446742</v>
       </c>
       <c r="R3" t="n">
-        <v>7167211</v>
+        <v>7167235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181587</v>
+        <v>120181606</v>
       </c>
       <c r="B2" t="n">
-        <v>78705</v>
+        <v>74586</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>1776</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446769</v>
+        <v>446711</v>
       </c>
       <c r="R2" t="n">
-        <v>7167211</v>
+        <v>7167230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181606</v>
+        <v>120181587</v>
       </c>
       <c r="B4" t="n">
-        <v>74586</v>
+        <v>78705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1776</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446711</v>
+        <v>446769</v>
       </c>
       <c r="R4" t="n">
-        <v>7167230</v>
+        <v>7167211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1376-2024 artfynd.xlsx
+++ b/artfynd/A 1376-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181984</v>
+        <v>120181587</v>
       </c>
       <c r="B3" t="n">
-        <v>74646</v>
+        <v>78705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446742</v>
+        <v>446769</v>
       </c>
       <c r="R3" t="n">
-        <v>7167235</v>
+        <v>7167211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181587</v>
+        <v>120181984</v>
       </c>
       <c r="B4" t="n">
-        <v>78705</v>
+        <v>74646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446769</v>
+        <v>446742</v>
       </c>
       <c r="R4" t="n">
-        <v>7167211</v>
+        <v>7167235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
